--- a/backend/downloads/미분양주택현황보고_규모별 미분양현황 (200701 ~ 202508).xlsx
+++ b/backend/downloads/미분양주택현황보고_규모별 미분양현황 (200701 ~ 202508).xlsx
@@ -169,7 +169,7 @@
     <row r="2" customHeight="true" ht="25.0">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>다운로드 시간 : 2025-10-14   10:03</t>
+          <t>다운로드 시간 : 2025-10-14   23:56</t>
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr">

--- a/backend/downloads/미분양주택현황보고_규모별 미분양현황 (200701 ~ 202508).xlsx
+++ b/backend/downloads/미분양주택현황보고_규모별 미분양현황 (200701 ~ 202508).xlsx
@@ -88,16 +88,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
       <alignment vertical="center" horizontal="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
       <alignment vertical="center" horizontal="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
-      <alignment vertical="center" horizontal="left" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
       <alignment vertical="center" horizontal="left" wrapText="true"/>
@@ -126,12 +123,11 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="70.77734375" customWidth="true"/>
-    <col min="2" max="2" width="41.70703125" customWidth="true"/>
-    <col min="3" max="3" width="41.70703125" customWidth="true"/>
-    <col min="4" max="4" width="41.70703125" customWidth="true"/>
-    <col min="5" max="5" width="41.70703125" customWidth="true"/>
-    <col min="6" max="6" width="83.59375" customWidth="true"/>
+    <col min="1" max="1" width="81.4296875" customWidth="true"/>
+    <col min="2" max="2" width="47.84375" customWidth="true"/>
+    <col min="3" max="3" width="47.84375" customWidth="true"/>
+    <col min="4" max="4" width="48.02734375" customWidth="true"/>
+    <col min="5" max="5" width="96.0546875" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1" customHeight="true" ht="25.0">
@@ -160,16 +156,11 @@
           <t/>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
     </row>
     <row r="2" customHeight="true" ht="25.0">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>다운로드 시간 : 2025-10-14   23:56</t>
+          <t>다운로드 시간 : 2025-10-15   10:04</t>
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr">
@@ -188,11 +179,6 @@
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -224,11 +210,6 @@
           <t>단위 : 호</t>
         </is>
       </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
     </row>
     <row r="4" customHeight="true" ht="25.0">
       <c r="A4" s="1" t="inlineStr">
@@ -256,11 +237,6 @@
           <t/>
         </is>
       </c>
-      <c r="F4" s="1" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
     </row>
     <row r="5" customHeight="true" ht="25.0">
       <c r="A5" s="2" t="inlineStr">
@@ -270,25 +246,20 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>구분</t>
+          <t>시도</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>시군구</t>
+          <t>부문</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>부문</t>
+          <t>규모</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>규모</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>호</t>
         </is>
@@ -317,10 +288,9 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>66613</t>
-        </is>
-      </c>
-      <c r="F6" s="8"/>
+          <t>66,613</t>
+        </is>
+      </c>
     </row>
     <row r="7" customHeight="true" ht="25.0">
       <c r="A7" s="3" t="inlineStr">
@@ -348,7 +318,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="8"/>
     </row>
     <row r="8" customHeight="true" ht="25.0">
       <c r="A8" s="3" t="inlineStr">
@@ -373,10 +342,9 @@
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>66613</t>
-        </is>
-      </c>
-      <c r="F8" s="8"/>
+          <t>66,613</t>
+        </is>
+      </c>
     </row>
     <row r="9" customHeight="true" ht="25.0">
       <c r="A9" s="3" t="inlineStr">
@@ -401,10 +369,9 @@
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>1932</t>
-        </is>
-      </c>
-      <c r="F9" s="8"/>
+          <t>1,932</t>
+        </is>
+      </c>
     </row>
     <row r="10" customHeight="true" ht="25.0">
       <c r="A10" s="3" t="inlineStr">
@@ -429,10 +396,9 @@
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>6111</t>
-        </is>
-      </c>
-      <c r="F10" s="8"/>
+          <t>6,111</t>
+        </is>
+      </c>
     </row>
     <row r="11" customHeight="true" ht="25.0">
       <c r="A11" s="3" t="inlineStr">
@@ -457,10 +423,9 @@
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>47209</t>
-        </is>
-      </c>
-      <c r="F11" s="8"/>
+          <t>47,209</t>
+        </is>
+      </c>
     </row>
     <row r="12" customHeight="true" ht="25.0">
       <c r="A12" s="3" t="inlineStr">
@@ -485,10 +450,9 @@
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>11361</t>
-        </is>
-      </c>
-      <c r="F12" s="8"/>
+          <t>11,361</t>
+        </is>
+      </c>
     </row>
     <row r="13" customHeight="true" ht="25.0">
       <c r="A13" s="3" t="inlineStr">
@@ -513,10 +477,9 @@
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>14631</t>
-        </is>
-      </c>
-      <c r="F13" s="8"/>
+          <t>14,631</t>
+        </is>
+      </c>
     </row>
     <row r="14" customHeight="true" ht="25.0">
       <c r="A14" s="3" t="inlineStr">
@@ -544,7 +507,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="8"/>
     </row>
     <row r="15" customHeight="true" ht="25.0">
       <c r="A15" s="3" t="inlineStr">
@@ -569,10 +531,9 @@
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>14631</t>
-        </is>
-      </c>
-      <c r="F15" s="8"/>
+          <t>14,631</t>
+        </is>
+      </c>
     </row>
     <row r="16" customHeight="true" ht="25.0">
       <c r="A16" s="3" t="inlineStr">
@@ -600,7 +561,6 @@
           <t>705</t>
         </is>
       </c>
-      <c r="F16" s="8"/>
     </row>
     <row r="17" customHeight="true" ht="25.0">
       <c r="A17" s="3" t="inlineStr">
@@ -625,10 +585,9 @@
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>1814</t>
-        </is>
-      </c>
-      <c r="F17" s="8"/>
+          <t>1,814</t>
+        </is>
+      </c>
     </row>
     <row r="18" customHeight="true" ht="25.0">
       <c r="A18" s="3" t="inlineStr">
@@ -653,10 +612,9 @@
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>10881</t>
-        </is>
-      </c>
-      <c r="F18" s="8"/>
+          <t>10,881</t>
+        </is>
+      </c>
     </row>
     <row r="19" customHeight="true" ht="25.0">
       <c r="A19" s="3" t="inlineStr">
@@ -681,10 +639,9 @@
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>1231</t>
-        </is>
-      </c>
-      <c r="F19" s="8"/>
+          <t>1,231</t>
+        </is>
+      </c>
     </row>
     <row r="20" customHeight="true" ht="25.0">
       <c r="A20" s="3" t="inlineStr">
@@ -709,10 +666,9 @@
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>1106</t>
-        </is>
-      </c>
-      <c r="F20" s="8"/>
+          <t>1,106</t>
+        </is>
+      </c>
     </row>
     <row r="21" customHeight="true" ht="25.0">
       <c r="A21" s="3" t="inlineStr">
@@ -740,7 +696,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F21" s="8"/>
     </row>
     <row r="22" customHeight="true" ht="25.0">
       <c r="A22" s="3" t="inlineStr">
@@ -765,10 +720,9 @@
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>1106</t>
-        </is>
-      </c>
-      <c r="F22" s="8"/>
+          <t>1,106</t>
+        </is>
+      </c>
     </row>
     <row r="23" customHeight="true" ht="25.0">
       <c r="A23" s="3" t="inlineStr">
@@ -796,7 +750,6 @@
           <t>337</t>
         </is>
       </c>
-      <c r="F23" s="8"/>
     </row>
     <row r="24" customHeight="true" ht="25.0">
       <c r="A24" s="3" t="inlineStr">
@@ -824,7 +777,6 @@
           <t>529</t>
         </is>
       </c>
-      <c r="F24" s="8"/>
     </row>
     <row r="25" customHeight="true" ht="25.0">
       <c r="A25" s="3" t="inlineStr">
@@ -852,7 +804,6 @@
           <t>196</t>
         </is>
       </c>
-      <c r="F25" s="8"/>
     </row>
     <row r="26" customHeight="true" ht="25.0">
       <c r="A26" s="3" t="inlineStr">
@@ -880,7 +831,6 @@
           <t>44</t>
         </is>
       </c>
-      <c r="F26" s="8"/>
     </row>
     <row r="27" customHeight="true" ht="25.0">
       <c r="A27" s="3" t="inlineStr">
@@ -905,10 +855,9 @@
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>7146</t>
-        </is>
-      </c>
-      <c r="F27" s="8"/>
+          <t>7,146</t>
+        </is>
+      </c>
     </row>
     <row r="28" customHeight="true" ht="25.0">
       <c r="A28" s="3" t="inlineStr">
@@ -936,7 +885,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F28" s="8"/>
     </row>
     <row r="29" customHeight="true" ht="25.0">
       <c r="A29" s="3" t="inlineStr">
@@ -961,10 +909,9 @@
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>7146</t>
-        </is>
-      </c>
-      <c r="F29" s="8"/>
+          <t>7,146</t>
+        </is>
+      </c>
     </row>
     <row r="30" customHeight="true" ht="25.0">
       <c r="A30" s="3" t="inlineStr">
@@ -992,7 +939,6 @@
           <t>170</t>
         </is>
       </c>
-      <c r="F30" s="8"/>
     </row>
     <row r="31" customHeight="true" ht="25.0">
       <c r="A31" s="3" t="inlineStr">
@@ -1017,10 +963,9 @@
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>1540</t>
-        </is>
-      </c>
-      <c r="F31" s="8"/>
+          <t>1,540</t>
+        </is>
+      </c>
     </row>
     <row r="32" customHeight="true" ht="25.0">
       <c r="A32" s="3" t="inlineStr">
@@ -1045,10 +990,9 @@
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>4063</t>
-        </is>
-      </c>
-      <c r="F32" s="8"/>
+          <t>4,063</t>
+        </is>
+      </c>
     </row>
     <row r="33" customHeight="true" ht="25.0">
       <c r="A33" s="3" t="inlineStr">
@@ -1073,10 +1017,9 @@
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>1373</t>
-        </is>
-      </c>
-      <c r="F33" s="8"/>
+          <t>1,373</t>
+        </is>
+      </c>
     </row>
     <row r="34" customHeight="true" ht="25.0">
       <c r="A34" s="3" t="inlineStr">
@@ -1101,10 +1044,9 @@
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>8762</t>
-        </is>
-      </c>
-      <c r="F34" s="8"/>
+          <t>8,762</t>
+        </is>
+      </c>
     </row>
     <row r="35" customHeight="true" ht="25.0">
       <c r="A35" s="3" t="inlineStr">
@@ -1132,7 +1074,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F35" s="8"/>
     </row>
     <row r="36" customHeight="true" ht="25.0">
       <c r="A36" s="3" t="inlineStr">
@@ -1157,10 +1098,9 @@
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>8762</t>
-        </is>
-      </c>
-      <c r="F36" s="8"/>
+          <t>8,762</t>
+        </is>
+      </c>
     </row>
     <row r="37" customHeight="true" ht="25.0">
       <c r="A37" s="3" t="inlineStr">
@@ -1188,7 +1128,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F37" s="8"/>
     </row>
     <row r="38" customHeight="true" ht="25.0">
       <c r="A38" s="3" t="inlineStr">
@@ -1216,7 +1155,6 @@
           <t>68</t>
         </is>
       </c>
-      <c r="F38" s="8"/>
     </row>
     <row r="39" customHeight="true" ht="25.0">
       <c r="A39" s="3" t="inlineStr">
@@ -1241,10 +1179,9 @@
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>6374</t>
-        </is>
-      </c>
-      <c r="F39" s="8"/>
+          <t>6,374</t>
+        </is>
+      </c>
     </row>
     <row r="40" customHeight="true" ht="25.0">
       <c r="A40" s="3" t="inlineStr">
@@ -1269,10 +1206,9 @@
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>2320</t>
-        </is>
-      </c>
-      <c r="F40" s="8"/>
+          <t>2,320</t>
+        </is>
+      </c>
     </row>
     <row r="41" customHeight="true" ht="25.0">
       <c r="A41" s="3" t="inlineStr">
@@ -1297,10 +1233,9 @@
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>1668</t>
-        </is>
-      </c>
-      <c r="F41" s="8"/>
+          <t>1,668</t>
+        </is>
+      </c>
     </row>
     <row r="42" customHeight="true" ht="25.0">
       <c r="A42" s="3" t="inlineStr">
@@ -1328,7 +1263,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F42" s="8"/>
     </row>
     <row r="43" customHeight="true" ht="25.0">
       <c r="A43" s="3" t="inlineStr">
@@ -1353,10 +1287,9 @@
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>1668</t>
-        </is>
-      </c>
-      <c r="F43" s="8"/>
+          <t>1,668</t>
+        </is>
+      </c>
     </row>
     <row r="44" customHeight="true" ht="25.0">
       <c r="A44" s="3" t="inlineStr">
@@ -1384,7 +1317,6 @@
           <t>28</t>
         </is>
       </c>
-      <c r="F44" s="8"/>
     </row>
     <row r="45" customHeight="true" ht="25.0">
       <c r="A45" s="3" t="inlineStr">
@@ -1412,7 +1344,6 @@
           <t>352</t>
         </is>
       </c>
-      <c r="F45" s="8"/>
     </row>
     <row r="46" customHeight="true" ht="25.0">
       <c r="A46" s="3" t="inlineStr">
@@ -1437,10 +1368,9 @@
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>1222</t>
-        </is>
-      </c>
-      <c r="F46" s="8"/>
+          <t>1,222</t>
+        </is>
+      </c>
     </row>
     <row r="47" customHeight="true" ht="25.0">
       <c r="A47" s="3" t="inlineStr">
@@ -1468,7 +1398,6 @@
           <t>66</t>
         </is>
       </c>
-      <c r="F47" s="8"/>
     </row>
     <row r="48" customHeight="true" ht="25.0">
       <c r="A48" s="3" t="inlineStr">
@@ -1493,10 +1422,9 @@
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>1370</t>
-        </is>
-      </c>
-      <c r="F48" s="8"/>
+          <t>1,370</t>
+        </is>
+      </c>
     </row>
     <row r="49" customHeight="true" ht="25.0">
       <c r="A49" s="3" t="inlineStr">
@@ -1524,7 +1452,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F49" s="8"/>
     </row>
     <row r="50" customHeight="true" ht="25.0">
       <c r="A50" s="3" t="inlineStr">
@@ -1549,10 +1476,9 @@
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>1370</t>
-        </is>
-      </c>
-      <c r="F50" s="8"/>
+          <t>1,370</t>
+        </is>
+      </c>
     </row>
     <row r="51" customHeight="true" ht="25.0">
       <c r="A51" s="3" t="inlineStr">
@@ -1580,7 +1506,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F51" s="8"/>
     </row>
     <row r="52" customHeight="true" ht="25.0">
       <c r="A52" s="3" t="inlineStr">
@@ -1608,7 +1533,6 @@
           <t>25</t>
         </is>
       </c>
-      <c r="F52" s="8"/>
     </row>
     <row r="53" customHeight="true" ht="25.0">
       <c r="A53" s="3" t="inlineStr">
@@ -1633,10 +1557,9 @@
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>1053</t>
-        </is>
-      </c>
-      <c r="F53" s="8"/>
+          <t>1,053</t>
+        </is>
+      </c>
     </row>
     <row r="54" customHeight="true" ht="25.0">
       <c r="A54" s="3" t="inlineStr">
@@ -1664,7 +1587,6 @@
           <t>292</t>
         </is>
       </c>
-      <c r="F54" s="8"/>
     </row>
     <row r="55" customHeight="true" ht="25.0">
       <c r="A55" s="3" t="inlineStr">
@@ -1689,10 +1611,9 @@
       </c>
       <c r="E55" s="7" t="inlineStr">
         <is>
-          <t>2485</t>
-        </is>
-      </c>
-      <c r="F55" s="8"/>
+          <t>2,485</t>
+        </is>
+      </c>
     </row>
     <row r="56" customHeight="true" ht="25.0">
       <c r="A56" s="3" t="inlineStr">
@@ -1720,7 +1641,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F56" s="8"/>
     </row>
     <row r="57" customHeight="true" ht="25.0">
       <c r="A57" s="3" t="inlineStr">
@@ -1745,10 +1665,9 @@
       </c>
       <c r="E57" s="7" t="inlineStr">
         <is>
-          <t>2485</t>
-        </is>
-      </c>
-      <c r="F57" s="8"/>
+          <t>2,485</t>
+        </is>
+      </c>
     </row>
     <row r="58" customHeight="true" ht="25.0">
       <c r="A58" s="3" t="inlineStr">
@@ -1776,7 +1695,6 @@
           <t>128</t>
         </is>
       </c>
-      <c r="F58" s="8"/>
     </row>
     <row r="59" customHeight="true" ht="25.0">
       <c r="A59" s="3" t="inlineStr">
@@ -1804,7 +1722,6 @@
           <t>393</t>
         </is>
       </c>
-      <c r="F59" s="8"/>
     </row>
     <row r="60" customHeight="true" ht="25.0">
       <c r="A60" s="3" t="inlineStr">
@@ -1829,10 +1746,9 @@
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>1586</t>
-        </is>
-      </c>
-      <c r="F60" s="8"/>
+          <t>1,586</t>
+        </is>
+      </c>
     </row>
     <row r="61" customHeight="true" ht="25.0">
       <c r="A61" s="3" t="inlineStr">
@@ -1860,7 +1776,6 @@
           <t>378</t>
         </is>
       </c>
-      <c r="F61" s="8"/>
     </row>
     <row r="62" customHeight="true" ht="25.0">
       <c r="A62" s="3" t="inlineStr">
@@ -1885,10 +1800,9 @@
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>2308</t>
-        </is>
-      </c>
-      <c r="F62" s="8"/>
+          <t>2,308</t>
+        </is>
+      </c>
     </row>
     <row r="63" customHeight="true" ht="25.0">
       <c r="A63" s="3" t="inlineStr">
@@ -1916,7 +1830,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F63" s="8"/>
     </row>
     <row r="64" customHeight="true" ht="25.0">
       <c r="A64" s="3" t="inlineStr">
@@ -1941,10 +1854,9 @@
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>2308</t>
-        </is>
-      </c>
-      <c r="F64" s="8"/>
+          <t>2,308</t>
+        </is>
+      </c>
     </row>
     <row r="65" customHeight="true" ht="25.0">
       <c r="A65" s="3" t="inlineStr">
@@ -1972,7 +1884,6 @@
           <t>23</t>
         </is>
       </c>
-      <c r="F65" s="8"/>
     </row>
     <row r="66" customHeight="true" ht="25.0">
       <c r="A66" s="3" t="inlineStr">
@@ -2000,7 +1911,6 @@
           <t>30</t>
         </is>
       </c>
-      <c r="F66" s="8"/>
     </row>
     <row r="67" customHeight="true" ht="25.0">
       <c r="A67" s="3" t="inlineStr">
@@ -2025,10 +1935,9 @@
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>1850</t>
-        </is>
-      </c>
-      <c r="F67" s="8"/>
+          <t>1,850</t>
+        </is>
+      </c>
     </row>
     <row r="68" customHeight="true" ht="25.0">
       <c r="A68" s="3" t="inlineStr">
@@ -2056,7 +1965,6 @@
           <t>405</t>
         </is>
       </c>
-      <c r="F68" s="8"/>
     </row>
     <row r="69" customHeight="true" ht="25.0">
       <c r="A69" s="3" t="inlineStr">
@@ -2081,10 +1989,9 @@
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>11857</t>
-        </is>
-      </c>
-      <c r="F69" s="8"/>
+          <t>11,857</t>
+        </is>
+      </c>
     </row>
     <row r="70" customHeight="true" ht="25.0">
       <c r="A70" s="3" t="inlineStr">
@@ -2112,7 +2019,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F70" s="8"/>
     </row>
     <row r="71" customHeight="true" ht="25.0">
       <c r="A71" s="3" t="inlineStr">
@@ -2137,10 +2043,9 @@
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
-          <t>11857</t>
-        </is>
-      </c>
-      <c r="F71" s="8"/>
+          <t>11,857</t>
+        </is>
+      </c>
     </row>
     <row r="72" customHeight="true" ht="25.0">
       <c r="A72" s="3" t="inlineStr">
@@ -2168,7 +2073,6 @@
           <t>340</t>
         </is>
       </c>
-      <c r="F72" s="8"/>
     </row>
     <row r="73" customHeight="true" ht="25.0">
       <c r="A73" s="3" t="inlineStr">
@@ -2196,7 +2100,6 @@
           <t>933</t>
         </is>
       </c>
-      <c r="F73" s="8"/>
     </row>
     <row r="74" customHeight="true" ht="25.0">
       <c r="A74" s="3" t="inlineStr">
@@ -2221,10 +2124,9 @@
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>9463</t>
-        </is>
-      </c>
-      <c r="F74" s="8"/>
+          <t>9,463</t>
+        </is>
+      </c>
     </row>
     <row r="75" customHeight="true" ht="25.0">
       <c r="A75" s="3" t="inlineStr">
@@ -2249,10 +2151,9 @@
       </c>
       <c r="E75" s="7" t="inlineStr">
         <is>
-          <t>1121</t>
-        </is>
-      </c>
-      <c r="F75" s="8"/>
+          <t>1,121</t>
+        </is>
+      </c>
     </row>
     <row r="76" customHeight="true" ht="25.0">
       <c r="A76" s="3" t="inlineStr">
@@ -2277,10 +2178,9 @@
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>3190</t>
-        </is>
-      </c>
-      <c r="F76" s="8"/>
+          <t>3,190</t>
+        </is>
+      </c>
     </row>
     <row r="77" customHeight="true" ht="25.0">
       <c r="A77" s="3" t="inlineStr">
@@ -2308,7 +2208,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F77" s="8"/>
     </row>
     <row r="78" customHeight="true" ht="25.0">
       <c r="A78" s="3" t="inlineStr">
@@ -2333,10 +2232,9 @@
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>3190</t>
-        </is>
-      </c>
-      <c r="F78" s="8"/>
+          <t>3,190</t>
+        </is>
+      </c>
     </row>
     <row r="79" customHeight="true" ht="25.0">
       <c r="A79" s="3" t="inlineStr">
@@ -2364,7 +2262,6 @@
           <t>85</t>
         </is>
       </c>
-      <c r="F79" s="8"/>
     </row>
     <row r="80" customHeight="true" ht="25.0">
       <c r="A80" s="3" t="inlineStr">
@@ -2392,7 +2289,6 @@
           <t>397</t>
         </is>
       </c>
-      <c r="F80" s="8"/>
     </row>
     <row r="81" customHeight="true" ht="25.0">
       <c r="A81" s="3" t="inlineStr">
@@ -2417,10 +2313,9 @@
       </c>
       <c r="E81" s="7" t="inlineStr">
         <is>
-          <t>2210</t>
-        </is>
-      </c>
-      <c r="F81" s="8"/>
+          <t>2,210</t>
+        </is>
+      </c>
     </row>
     <row r="82" customHeight="true" ht="25.0">
       <c r="A82" s="3" t="inlineStr">
@@ -2448,7 +2343,6 @@
           <t>498</t>
         </is>
       </c>
-      <c r="F82" s="8"/>
     </row>
     <row r="83" customHeight="true" ht="25.0">
       <c r="A83" s="3" t="inlineStr">
@@ -2473,10 +2367,9 @@
       </c>
       <c r="E83" s="7" t="inlineStr">
         <is>
-          <t>1912</t>
-        </is>
-      </c>
-      <c r="F83" s="8"/>
+          <t>1,912</t>
+        </is>
+      </c>
     </row>
     <row r="84" customHeight="true" ht="25.0">
       <c r="A84" s="3" t="inlineStr">
@@ -2504,7 +2397,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F84" s="8"/>
     </row>
     <row r="85" customHeight="true" ht="25.0">
       <c r="A85" s="3" t="inlineStr">
@@ -2529,10 +2421,9 @@
       </c>
       <c r="E85" s="7" t="inlineStr">
         <is>
-          <t>1912</t>
-        </is>
-      </c>
-      <c r="F85" s="8"/>
+          <t>1,912</t>
+        </is>
+      </c>
     </row>
     <row r="86" customHeight="true" ht="25.0">
       <c r="A86" s="3" t="inlineStr">
@@ -2560,7 +2451,6 @@
           <t>103</t>
         </is>
       </c>
-      <c r="F86" s="8"/>
     </row>
     <row r="87" customHeight="true" ht="25.0">
       <c r="A87" s="3" t="inlineStr">
@@ -2588,7 +2478,6 @@
           <t>186</t>
         </is>
       </c>
-      <c r="F87" s="8"/>
     </row>
     <row r="88" customHeight="true" ht="25.0">
       <c r="A88" s="3" t="inlineStr">
@@ -2613,10 +2502,9 @@
       </c>
       <c r="E88" s="7" t="inlineStr">
         <is>
-          <t>1359</t>
-        </is>
-      </c>
-      <c r="F88" s="8"/>
+          <t>1,359</t>
+        </is>
+      </c>
     </row>
     <row r="89" customHeight="true" ht="25.0">
       <c r="A89" s="3" t="inlineStr">
@@ -2644,7 +2532,6 @@
           <t>264</t>
         </is>
       </c>
-      <c r="F89" s="8"/>
     </row>
     <row r="90" customHeight="true" ht="25.0">
       <c r="A90" s="3" t="inlineStr">
@@ -2669,10 +2556,9 @@
       </c>
       <c r="E90" s="7" t="inlineStr">
         <is>
-          <t>5499</t>
-        </is>
-      </c>
-      <c r="F90" s="8"/>
+          <t>5,499</t>
+        </is>
+      </c>
     </row>
     <row r="91" customHeight="true" ht="25.0">
       <c r="A91" s="3" t="inlineStr">
@@ -2700,7 +2586,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F91" s="8"/>
     </row>
     <row r="92" customHeight="true" ht="25.0">
       <c r="A92" s="3" t="inlineStr">
@@ -2725,10 +2610,9 @@
       </c>
       <c r="E92" s="7" t="inlineStr">
         <is>
-          <t>5499</t>
-        </is>
-      </c>
-      <c r="F92" s="8"/>
+          <t>5,499</t>
+        </is>
+      </c>
     </row>
     <row r="93" customHeight="true" ht="25.0">
       <c r="A93" s="3" t="inlineStr">
@@ -2756,7 +2640,6 @@
           <t>335</t>
         </is>
       </c>
-      <c r="F93" s="8"/>
     </row>
     <row r="94" customHeight="true" ht="25.0">
       <c r="A94" s="3" t="inlineStr">
@@ -2784,7 +2667,6 @@
           <t>122</t>
         </is>
       </c>
-      <c r="F94" s="8"/>
     </row>
     <row r="95" customHeight="true" ht="25.0">
       <c r="A95" s="3" t="inlineStr">
@@ -2809,10 +2691,9 @@
       </c>
       <c r="E95" s="7" t="inlineStr">
         <is>
-          <t>4358</t>
-        </is>
-      </c>
-      <c r="F95" s="8"/>
+          <t>4,358</t>
+        </is>
+      </c>
     </row>
     <row r="96" customHeight="true" ht="25.0">
       <c r="A96" s="3" t="inlineStr">
@@ -2840,7 +2721,6 @@
           <t>684</t>
         </is>
       </c>
-      <c r="F96" s="8"/>
     </row>
     <row r="97" customHeight="true" ht="25.0">
       <c r="A97" s="3" t="inlineStr">
@@ -2868,7 +2748,6 @@
           <t>50</t>
         </is>
       </c>
-      <c r="F97" s="8"/>
     </row>
     <row r="98" customHeight="true" ht="25.0">
       <c r="A98" s="3" t="inlineStr">
@@ -2896,7 +2775,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F98" s="8"/>
     </row>
     <row r="99" customHeight="true" ht="25.0">
       <c r="A99" s="3" t="inlineStr">
@@ -2924,7 +2802,6 @@
           <t>50</t>
         </is>
       </c>
-      <c r="F99" s="8"/>
     </row>
     <row r="100" customHeight="true" ht="25.0">
       <c r="A100" s="3" t="inlineStr">
@@ -2952,7 +2829,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F100" s="8"/>
     </row>
     <row r="101" customHeight="true" ht="25.0">
       <c r="A101" s="3" t="inlineStr">
@@ -2980,7 +2856,6 @@
           <t>29</t>
         </is>
       </c>
-      <c r="F101" s="8"/>
     </row>
     <row r="102" customHeight="true" ht="25.0">
       <c r="A102" s="3" t="inlineStr">
@@ -3008,7 +2883,6 @@
           <t>21</t>
         </is>
       </c>
-      <c r="F102" s="8"/>
     </row>
     <row r="103" customHeight="true" ht="25.0">
       <c r="A103" s="3" t="inlineStr">
@@ -3036,7 +2910,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F103" s="8"/>
     </row>
     <row r="104" customHeight="true" ht="25.0">
       <c r="A104" s="3" t="inlineStr">
@@ -3061,10 +2934,9 @@
       </c>
       <c r="E104" s="7" t="inlineStr">
         <is>
-          <t>2694</t>
-        </is>
-      </c>
-      <c r="F104" s="8"/>
+          <t>2,694</t>
+        </is>
+      </c>
     </row>
     <row r="105" customHeight="true" ht="25.0">
       <c r="A105" s="3" t="inlineStr">
@@ -3092,7 +2964,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F105" s="8"/>
     </row>
     <row r="106" customHeight="true" ht="25.0">
       <c r="A106" s="3" t="inlineStr">
@@ -3117,10 +2988,9 @@
       </c>
       <c r="E106" s="7" t="inlineStr">
         <is>
-          <t>2694</t>
-        </is>
-      </c>
-      <c r="F106" s="8"/>
+          <t>2,694</t>
+        </is>
+      </c>
     </row>
     <row r="107" customHeight="true" ht="25.0">
       <c r="A107" s="3" t="inlineStr">
@@ -3148,7 +3018,6 @@
           <t>43</t>
         </is>
       </c>
-      <c r="F107" s="8"/>
     </row>
     <row r="108" customHeight="true" ht="25.0">
       <c r="A108" s="3" t="inlineStr">
@@ -3176,7 +3045,6 @@
           <t>90</t>
         </is>
       </c>
-      <c r="F108" s="8"/>
     </row>
     <row r="109" customHeight="true" ht="25.0">
       <c r="A109" s="3" t="inlineStr">
@@ -3201,10 +3069,9 @@
       </c>
       <c r="E109" s="7" t="inlineStr">
         <is>
-          <t>1942</t>
-        </is>
-      </c>
-      <c r="F109" s="8"/>
+          <t>1,942</t>
+        </is>
+      </c>
     </row>
     <row r="110" customHeight="true" ht="25.0">
       <c r="A110" s="3" t="inlineStr">
@@ -3232,7 +3099,6 @@
           <t>619</t>
         </is>
       </c>
-      <c r="F110" s="8"/>
     </row>
     <row r="111" customHeight="true" ht="25.0">
       <c r="A111" s="3" t="inlineStr">
@@ -3257,10 +3123,9 @@
       </c>
       <c r="E111" s="7" t="inlineStr">
         <is>
-          <t>2828</t>
-        </is>
-      </c>
-      <c r="F111" s="8"/>
+          <t>2,828</t>
+        </is>
+      </c>
     </row>
     <row r="112" customHeight="true" ht="25.0">
       <c r="A112" s="3" t="inlineStr">
@@ -3288,7 +3153,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F112" s="8"/>
     </row>
     <row r="113" customHeight="true" ht="25.0">
       <c r="A113" s="3" t="inlineStr">
@@ -3313,10 +3177,9 @@
       </c>
       <c r="E113" s="7" t="inlineStr">
         <is>
-          <t>2828</t>
-        </is>
-      </c>
-      <c r="F113" s="8"/>
+          <t>2,828</t>
+        </is>
+      </c>
     </row>
     <row r="114" customHeight="true" ht="25.0">
       <c r="A114" s="3" t="inlineStr">
@@ -3344,7 +3207,6 @@
           <t>238</t>
         </is>
       </c>
-      <c r="F114" s="8"/>
     </row>
     <row r="115" customHeight="true" ht="25.0">
       <c r="A115" s="3" t="inlineStr">
@@ -3372,7 +3234,6 @@
           <t>158</t>
         </is>
       </c>
-      <c r="F115" s="8"/>
     </row>
     <row r="116" customHeight="true" ht="25.0">
       <c r="A116" s="3" t="inlineStr">
@@ -3397,10 +3258,9 @@
       </c>
       <c r="E116" s="7" t="inlineStr">
         <is>
-          <t>2170</t>
-        </is>
-      </c>
-      <c r="F116" s="8"/>
+          <t>2,170</t>
+        </is>
+      </c>
     </row>
     <row r="117" customHeight="true" ht="25.0">
       <c r="A117" s="3" t="inlineStr">
@@ -3428,7 +3288,6 @@
           <t>262</t>
         </is>
       </c>
-      <c r="F117" s="8"/>
     </row>
     <row r="118" customHeight="true" ht="25.0">
       <c r="A118" s="3" t="inlineStr">
@@ -3453,10 +3312,9 @@
       </c>
       <c r="E118" s="7" t="inlineStr">
         <is>
-          <t>6124</t>
-        </is>
-      </c>
-      <c r="F118" s="8"/>
+          <t>6,124</t>
+        </is>
+      </c>
     </row>
     <row r="119" customHeight="true" ht="25.0">
       <c r="A119" s="3" t="inlineStr">
@@ -3484,7 +3342,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F119" s="8"/>
     </row>
     <row r="120" customHeight="true" ht="25.0">
       <c r="A120" s="3" t="inlineStr">
@@ -3509,10 +3366,9 @@
       </c>
       <c r="E120" s="7" t="inlineStr">
         <is>
-          <t>6124</t>
-        </is>
-      </c>
-      <c r="F120" s="8"/>
+          <t>6,124</t>
+        </is>
+      </c>
     </row>
     <row r="121" customHeight="true" ht="25.0">
       <c r="A121" s="3" t="inlineStr">
@@ -3540,7 +3396,6 @@
           <t>66</t>
         </is>
       </c>
-      <c r="F121" s="8"/>
     </row>
     <row r="122" customHeight="true" ht="25.0">
       <c r="A122" s="3" t="inlineStr">
@@ -3568,7 +3423,6 @@
           <t>350</t>
         </is>
       </c>
-      <c r="F122" s="8"/>
     </row>
     <row r="123" customHeight="true" ht="25.0">
       <c r="A123" s="3" t="inlineStr">
@@ -3593,10 +3447,9 @@
       </c>
       <c r="E123" s="7" t="inlineStr">
         <is>
-          <t>4421</t>
-        </is>
-      </c>
-      <c r="F123" s="8"/>
+          <t>4,421</t>
+        </is>
+      </c>
     </row>
     <row r="124" customHeight="true" ht="25.0">
       <c r="A124" s="3" t="inlineStr">
@@ -3621,10 +3474,9 @@
       </c>
       <c r="E124" s="7" t="inlineStr">
         <is>
-          <t>1287</t>
-        </is>
-      </c>
-      <c r="F124" s="8"/>
+          <t>1,287</t>
+        </is>
+      </c>
     </row>
     <row r="125" customHeight="true" ht="25.0">
       <c r="A125" s="3" t="inlineStr">
@@ -3649,10 +3501,9 @@
       </c>
       <c r="E125" s="7" t="inlineStr">
         <is>
-          <t>4993</t>
-        </is>
-      </c>
-      <c r="F125" s="8"/>
+          <t>4,993</t>
+        </is>
+      </c>
     </row>
     <row r="126" customHeight="true" ht="25.0">
       <c r="A126" s="3" t="inlineStr">
@@ -3680,7 +3531,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F126" s="8"/>
     </row>
     <row r="127" customHeight="true" ht="25.0">
       <c r="A127" s="3" t="inlineStr">
@@ -3705,10 +3555,9 @@
       </c>
       <c r="E127" s="7" t="inlineStr">
         <is>
-          <t>4993</t>
-        </is>
-      </c>
-      <c r="F127" s="8"/>
+          <t>4,993</t>
+        </is>
+      </c>
     </row>
     <row r="128" customHeight="true" ht="25.0">
       <c r="A128" s="3" t="inlineStr">
@@ -3736,7 +3585,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F128" s="8"/>
     </row>
     <row r="129" customHeight="true" ht="25.0">
       <c r="A129" s="3" t="inlineStr">
@@ -3764,7 +3612,6 @@
           <t>768</t>
         </is>
       </c>
-      <c r="F129" s="8"/>
     </row>
     <row r="130" customHeight="true" ht="25.0">
       <c r="A130" s="3" t="inlineStr">
@@ -3789,10 +3636,9 @@
       </c>
       <c r="E130" s="7" t="inlineStr">
         <is>
-          <t>3641</t>
-        </is>
-      </c>
-      <c r="F130" s="8"/>
+          <t>3,641</t>
+        </is>
+      </c>
     </row>
     <row r="131" customHeight="true" ht="25.0">
       <c r="A131" s="3" t="inlineStr">
@@ -3820,7 +3666,6 @@
           <t>584</t>
         </is>
       </c>
-      <c r="F131" s="8"/>
     </row>
     <row r="132" customHeight="true" ht="25.0">
       <c r="A132" s="3" t="inlineStr">
@@ -3845,10 +3690,9 @@
       </c>
       <c r="E132" s="7" t="inlineStr">
         <is>
-          <t>2621</t>
-        </is>
-      </c>
-      <c r="F132" s="8"/>
+          <t>2,621</t>
+        </is>
+      </c>
     </row>
     <row r="133" customHeight="true" ht="25.0">
       <c r="A133" s="3" t="inlineStr">
@@ -3876,7 +3720,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F133" s="8"/>
     </row>
     <row r="134" customHeight="true" ht="25.0">
       <c r="A134" s="3" t="inlineStr">
@@ -3901,10 +3744,9 @@
       </c>
       <c r="E134" s="7" t="inlineStr">
         <is>
-          <t>2621</t>
-        </is>
-      </c>
-      <c r="F134" s="8"/>
+          <t>2,621</t>
+        </is>
+      </c>
     </row>
     <row r="135" customHeight="true" ht="25.0">
       <c r="A135" s="3" t="inlineStr">
@@ -3932,7 +3774,6 @@
           <t>36</t>
         </is>
       </c>
-      <c r="F135" s="8"/>
     </row>
     <row r="136" customHeight="true" ht="25.0">
       <c r="A136" s="3" t="inlineStr">
@@ -3960,7 +3801,6 @@
           <t>141</t>
         </is>
       </c>
-      <c r="F136" s="8"/>
     </row>
     <row r="137" customHeight="true" ht="25.0">
       <c r="A137" s="3" t="inlineStr">
@@ -3985,10 +3825,9 @@
       </c>
       <c r="E137" s="7" t="inlineStr">
         <is>
-          <t>1280</t>
-        </is>
-      </c>
-      <c r="F137" s="8"/>
+          <t>1,280</t>
+        </is>
+      </c>
     </row>
     <row r="138" customHeight="true" ht="25.0">
       <c r="A138" s="3" t="inlineStr">
@@ -4013,10 +3852,9 @@
       </c>
       <c r="E138" s="7" t="inlineStr">
         <is>
-          <t>1164</t>
-        </is>
-      </c>
-      <c r="F138" s="8"/>
+          <t>1,164</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells>

--- a/backend/downloads/미분양주택현황보고_규모별 미분양현황 (200701 ~ 202508).xlsx
+++ b/backend/downloads/미분양주택현황보고_규모별 미분양현황 (200701 ~ 202508).xlsx
@@ -160,7 +160,7 @@
     <row r="2" customHeight="true" ht="25.0">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>다운로드 시간 : 2025-10-15   10:04</t>
+          <t>다운로드 시간 : 2025-10-17   03:00</t>
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr">
